--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hi\OneDrive\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{FC7BEABA-F66B-47F3-9987-97BBCEB7092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{160E75E5-4A55-485A-9769-08FACF01ABDC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,18 @@
   </si>
   <si>
     <t>today  I learn javascript as extra skill</t>
+  </si>
+  <si>
+    <t>enroll in code flux</t>
+  </si>
+  <si>
+    <t>give CA of SQL</t>
+  </si>
+  <si>
+    <t>excited for giving first tym CA</t>
+  </si>
+  <si>
+    <t>due to household chores, I could not focus on my studies.</t>
   </si>
 </sst>
 </file>
@@ -2124,92 +2136,188 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>180</v>
+      </c>
+      <c r="F29" s="14">
+        <v>150</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14">
+        <v>90</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B30" s="14">
+        <v>360</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>120</v>
+      </c>
+      <c r="F31" s="14">
+        <v>50</v>
+      </c>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>45</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>695</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>745</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B32" s="14">
+        <v>480</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>150</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hi\OneDrive\Desktop\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38594DF9-CE02-41C8-8675-61AEB4DDFA13}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>due to household chores, I could not focus on my studies.</t>
+  </si>
+  <si>
+    <t>today I cover physical layer of networking.</t>
   </si>
 </sst>
 </file>
@@ -2319,27 +2322,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B33" s="14">
+        <v>270</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>300</v>
+      </c>
+      <c r="E33" s="14">
+        <v>120</v>
+      </c>
+      <c r="F33" s="14">
+        <v>250</v>
+      </c>
+      <c r="G33" s="14">
+        <v>5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>90</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38594DF9-CE02-41C8-8675-61AEB4DDFA13}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13336642-F5F7-4D9F-A4B6-9B41D2914DCB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>today I cover physical layer of networking.</t>
+  </si>
+  <si>
+    <t>today I felt sleepy in classes because I study last overnight.</t>
   </si>
 </sst>
 </file>
@@ -2368,27 +2371,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B34" s="14">
+        <v>480</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>90</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>100</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13336642-F5F7-4D9F-A4B6-9B41D2914DCB}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8112A5C6-4CCD-4E41-A270-FB0004D53101}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>today I felt sleepy in classes because I study last overnight.</t>
+  </si>
+  <si>
+    <t>attend freshers at LPU.</t>
   </si>
 </sst>
 </file>
@@ -2418,26 +2421,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B35" s="14">
+        <v>390</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>90</v>
+      </c>
+      <c r="F35" s="14">
+        <v>50</v>
+      </c>
+      <c r="G35" s="14">
+        <v>1</v>
+      </c>
+      <c r="H35" s="14">
+        <v>240</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8112A5C6-4CCD-4E41-A270-FB0004D53101}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA51B675-9F65-42D5-A9D5-F7E70732E585}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,15 @@
   </si>
   <si>
     <t>attend freshers at LPU.</t>
+  </si>
+  <si>
+    <t>ateend classes and celebrate my friend's birthday.</t>
+  </si>
+  <si>
+    <t>paticipate in hackthon</t>
+  </si>
+  <si>
+    <t>after completing 1st round of hackthon, I slept most of the day.</t>
   </si>
 </sst>
 </file>
@@ -2437,21 +2446,21 @@
         <v>90</v>
       </c>
       <c r="F35" s="14">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G35" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H35" s="14">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>49</v>
@@ -2466,74 +2475,148 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+    <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B36" s="14">
+        <v>360</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>90</v>
+      </c>
+      <c r="E36" s="14">
+        <v>180</v>
+      </c>
+      <c r="F36" s="14">
+        <v>50</v>
+      </c>
+      <c r="G36" s="14">
+        <v>1</v>
+      </c>
+      <c r="H36" s="14">
+        <v>240</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B37" s="14">
+        <v>180</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <v>270</v>
+      </c>
+      <c r="F37" s="14">
+        <v>100</v>
+      </c>
+      <c r="G37" s="14">
+        <v>2</v>
+      </c>
+      <c r="H37" s="14">
+        <v>480</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>410</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B38" s="14">
+        <v>360</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>90</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>360</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
+      <c r="A39" s="13">
+        <v>46278</v>
+      </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA51B675-9F65-42D5-A9D5-F7E70732E585}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A126A1DB-4F8A-445E-872D-30A0623EAFF8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,12 @@
   </si>
   <si>
     <t>after completing 1st round of hackthon, I slept most of the day.</t>
+  </si>
+  <si>
+    <t>I feel good .</t>
+  </si>
+  <si>
+    <t>it was a productive day.</t>
   </si>
 </sst>
 </file>
@@ -2617,47 +2623,93 @@
       <c r="A39" s="13">
         <v>46278</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="B39" s="14">
+        <v>360</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>100</v>
+      </c>
+      <c r="E39" s="14">
+        <v>270</v>
+      </c>
+      <c r="F39" s="14">
+        <v>250</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14">
+        <v>100</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B40" s="14">
+        <v>360</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>180</v>
+      </c>
+      <c r="E40" s="14">
+        <v>180</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>100</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hi\OneDrive\Desktop\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{086A9DC0-6D28-4C01-B6E1-86E0A490ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A126A1DB-4F8A-445E-872D-30A0623EAFF8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,9 +280,6 @@
     <t>again attend classes and in evening I felt so hungry.</t>
   </si>
   <si>
-    <t>SEPTEMBER</t>
-  </si>
-  <si>
     <t>full energetic to learn new things</t>
   </si>
   <si>
@@ -323,6 +320,27 @@
   </si>
   <si>
     <t>it was a productive day.</t>
+  </si>
+  <si>
+    <t>august</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>I feel relaxed while styding in library.</t>
+  </si>
+  <si>
+    <t>feel so tried.</t>
+  </si>
+  <si>
+    <t>lazy day.</t>
+  </si>
+  <si>
+    <t>it was a good day.</t>
+  </si>
+  <si>
+    <t>today it was analytical CA.</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1053,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -2110,7 +2128,7 @@
         <v>57</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2156,7 +2174,7 @@
         <v>57</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -2202,7 +2220,7 @@
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
@@ -2248,7 +2266,7 @@
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
@@ -2294,7 +2312,7 @@
         <v>51</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2340,7 +2358,7 @@
         <v>66</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2386,7 +2404,7 @@
         <v>57</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2432,7 +2450,7 @@
         <v>51</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
@@ -2478,7 +2496,7 @@
         <v>57</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2524,7 +2542,7 @@
         <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
@@ -2570,7 +2588,7 @@
         <v>57</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -2616,7 +2634,7 @@
         <v>66</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
@@ -2636,21 +2654,21 @@
         <v>270</v>
       </c>
       <c r="F39" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G39" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H39" s="14">
         <v>100</v>
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>830</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>610</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>56</v>
@@ -2662,7 +2680,7 @@
         <v>57</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
@@ -2682,21 +2700,21 @@
         <v>180</v>
       </c>
       <c r="F40" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G40" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H40" s="14">
         <v>100</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1070</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>370</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>58</v>
@@ -2708,118 +2726,238 @@
         <v>51</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B41" s="14">
+        <v>280</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>180</v>
+      </c>
+      <c r="E41" s="14">
+        <v>180</v>
+      </c>
+      <c r="F41" s="14">
+        <v>350</v>
+      </c>
+      <c r="G41" s="14">
+        <v>7</v>
+      </c>
+      <c r="H41" s="14">
+        <v>0</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B42" s="14">
+        <v>360</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>200</v>
+      </c>
+      <c r="E42" s="14">
+        <v>90</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>6</v>
+      </c>
+      <c r="H42" s="14">
+        <v>180</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B43" s="14">
+        <v>360</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>380</v>
+      </c>
+      <c r="E43" s="14">
+        <v>100</v>
+      </c>
+      <c r="F43" s="14">
+        <v>150</v>
+      </c>
+      <c r="G43" s="14">
+        <v>3</v>
+      </c>
+      <c r="H43" s="14">
+        <v>90</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B44" s="14">
+        <v>200</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>250</v>
+      </c>
+      <c r="E44" s="14">
+        <v>150</v>
+      </c>
+      <c r="F44" s="14">
+        <v>300</v>
+      </c>
+      <c r="G44" s="14">
+        <v>6</v>
+      </c>
+      <c r="H44" s="14">
+        <v>120</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B45" s="14">
+        <v>270</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>150</v>
+      </c>
+      <c r="E45" s="14">
+        <v>210</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>0</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hi\OneDrive\Desktop\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D8B2A0B-81EC-4F76-86F3-D2CAE09E0278}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>today it was analytical CA.</t>
+  </si>
+  <si>
+    <t>I met my dad and sister.</t>
   </si>
 </sst>
 </file>
@@ -2960,26 +2963,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B46" s="14">
+        <v>400</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>240</v>
+      </c>
+      <c r="E46" s="14">
+        <v>180</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>0</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D8B2A0B-81EC-4F76-86F3-D2CAE09E0278}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F62EEC81-BD5E-41C3-9D0B-A5B996530262}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>I met my dad and sister.</t>
+  </si>
+  <si>
+    <t>it was a hard day.</t>
   </si>
 </sst>
 </file>
@@ -3009,26 +3012,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B47" s="14">
+        <v>300</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>180</v>
+      </c>
+      <c r="E47" s="14">
+        <v>240</v>
+      </c>
+      <c r="F47" s="14">
+        <v>250</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>90</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F62EEC81-BD5E-41C3-9D0B-A5B996530262}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BA5D806-503A-497B-BEC5-BF9A971BEE60}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>it was a hard day.</t>
+  </si>
+  <si>
+    <t>face some family problems.</t>
   </si>
 </sst>
 </file>
@@ -3058,26 +3061,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B48" s="14">
+        <v>450</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>200</v>
+      </c>
+      <c r="E48" s="14">
+        <v>120</v>
+      </c>
+      <c r="F48" s="14">
+        <v>350</v>
+      </c>
+      <c r="G48" s="14">
+        <v>7</v>
+      </c>
+      <c r="H48" s="14">
+        <v>90</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BA5D806-503A-497B-BEC5-BF9A971BEE60}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{553B8BDA-7FDA-4D78-91CD-9EA105D5E6CF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,12 @@
   </si>
   <si>
     <t>face some family problems.</t>
+  </si>
+  <si>
+    <t>energy level high</t>
+  </si>
+  <si>
+    <t>start preparation of mid term.</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1280,7 @@
         <v>420</v>
       </c>
       <c r="C9" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D9" s="14">
         <v>120</v>
@@ -1293,11 +1299,11 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>56</v>
@@ -1320,7 +1326,7 @@
         <v>420</v>
       </c>
       <c r="C10" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D10" s="14">
         <v>240</v>
@@ -1339,11 +1345,11 @@
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
@@ -1366,7 +1372,7 @@
         <v>480</v>
       </c>
       <c r="C11" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="14">
         <v>180</v>
@@ -1385,11 +1391,11 @@
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>49</v>
@@ -1596,7 +1602,7 @@
         <v>360</v>
       </c>
       <c r="C16" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D16" s="14">
         <v>120</v>
@@ -1615,11 +1621,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>56</v>
@@ -1688,7 +1694,7 @@
         <v>420</v>
       </c>
       <c r="C18" s="14">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D18" s="14">
         <v>180</v>
@@ -1707,11 +1713,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>905</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>535</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>56</v>
@@ -1734,7 +1740,7 @@
         <v>360</v>
       </c>
       <c r="C19" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
         <v>120</v>
@@ -1753,11 +1759,11 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>56</v>
@@ -2056,7 +2062,7 @@
         <v>360</v>
       </c>
       <c r="C26" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
         <v>120</v>
@@ -2075,11 +2081,11 @@
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>58</v>
@@ -2102,7 +2108,7 @@
         <v>360</v>
       </c>
       <c r="C27" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D27" s="14">
         <v>180</v>
@@ -2121,11 +2127,11 @@
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>56</v>
@@ -2148,7 +2154,7 @@
         <v>360</v>
       </c>
       <c r="C28" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>170</v>
@@ -2167,11 +2173,11 @@
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>56</v>
@@ -2194,7 +2200,7 @@
         <v>360</v>
       </c>
       <c r="C29" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D29" s="14">
         <v>120</v>
@@ -2213,11 +2219,11 @@
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>
@@ -2286,7 +2292,7 @@
         <v>360</v>
       </c>
       <c r="C31" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D31" s="14">
         <v>120</v>
@@ -2305,11 +2311,11 @@
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>49</v>
@@ -2378,7 +2384,7 @@
         <v>270</v>
       </c>
       <c r="C33" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D33" s="14">
         <v>300</v>
@@ -2397,11 +2403,11 @@
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>1050</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>49</v>
@@ -2470,7 +2476,7 @@
         <v>390</v>
       </c>
       <c r="C35" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D35" s="14">
         <v>120</v>
@@ -2489,11 +2495,11 @@
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>49</v>
@@ -2562,7 +2568,7 @@
         <v>180</v>
       </c>
       <c r="C37" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D37" s="14">
         <v>0</v>
@@ -2581,11 +2587,11 @@
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>1045</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>58</v>
@@ -2654,7 +2660,7 @@
         <v>360</v>
       </c>
       <c r="C39" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D39" s="14">
         <v>100</v>
@@ -2673,11 +2679,11 @@
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>855</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>56</v>
@@ -2746,7 +2752,7 @@
         <v>280</v>
       </c>
       <c r="C41" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D41" s="14">
         <v>180</v>
@@ -2765,11 +2771,11 @@
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>49</v>
@@ -2792,7 +2798,7 @@
         <v>360</v>
       </c>
       <c r="C42" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D42" s="14">
         <v>200</v>
@@ -2811,11 +2817,11 @@
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1145</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>49</v>
@@ -2930,7 +2936,7 @@
         <v>270</v>
       </c>
       <c r="C45" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D45" s="14">
         <v>150</v>
@@ -2949,11 +2955,11 @@
       </c>
       <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v>630</v>
+        <v>645</v>
       </c>
       <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="K45" s="16" t="s">
         <v>96</v>
@@ -3068,7 +3074,7 @@
         <v>450</v>
       </c>
       <c r="C48" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D48" s="14">
         <v>200</v>
@@ -3087,11 +3093,11 @@
       </c>
       <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v>1210</v>
+        <v>1230</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>49</v>
@@ -3107,51 +3113,101 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B49" s="14">
+        <v>350</v>
+      </c>
+      <c r="C49" s="14">
+        <v>10</v>
+      </c>
+      <c r="D49" s="14">
+        <v>350</v>
+      </c>
+      <c r="E49" s="14">
+        <v>180</v>
+      </c>
+      <c r="F49" s="14">
+        <v>300</v>
+      </c>
+      <c r="G49" s="14">
+        <v>6</v>
+      </c>
+      <c r="H49" s="14">
+        <v>100</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B50" s="14">
+        <v>290</v>
+      </c>
+      <c r="C50" s="14">
+        <v>15</v>
+      </c>
+      <c r="D50" s="14">
+        <v>380</v>
+      </c>
+      <c r="E50" s="14">
+        <v>180</v>
+      </c>
+      <c r="F50" s="14">
+        <v>100</v>
+      </c>
+      <c r="G50" s="14">
+        <v>2</v>
+      </c>
+      <c r="H50" s="14">
+        <v>250</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1215</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>225</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
+      <c r="A51" s="13">
+        <v>46290</v>
+      </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>

--- a/12628918.xlsx
+++ b/12628918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b1e7fc98125237/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{553B8BDA-7FDA-4D78-91CD-9EA105D5E6CF}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{0FA85F2F-6758-4D12-9445-36FF3C7882F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C8E4CCE-B3D7-40D6-9888-CD3A4EAF2722}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>start preparation of mid term.</t>
+  </si>
+  <si>
+    <t>I met my best friend after long time .</t>
   </si>
 </sst>
 </file>
@@ -3204,29 +3207,51 @@
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="13">
         <v>46290</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="B51" s="14">
+        <v>280</v>
+      </c>
+      <c r="C51" s="14">
+        <v>20</v>
+      </c>
+      <c r="D51" s="14">
+        <v>240</v>
+      </c>
+      <c r="E51" s="14">
+        <v>180</v>
+      </c>
+      <c r="F51" s="14">
+        <v>300</v>
+      </c>
+      <c r="G51" s="14">
+        <v>6</v>
+      </c>
+      <c r="H51" s="14">
+        <v>100</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>
